--- a/data/trans_dic/P16A_n_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,34; 20,35</t>
+          <t>13,63; 20,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,92; 25,48</t>
+          <t>17,05; 25,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,83; 26,47</t>
+          <t>18,02; 26,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,16; 32,09</t>
+          <t>24,08; 32,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,27; 27,37</t>
+          <t>17,69; 27,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,68; 30,43</t>
+          <t>19,59; 30,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,74; 26,84</t>
+          <t>17,77; 26,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,92; 35,16</t>
+          <t>27,83; 35,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,14; 21,98</t>
+          <t>16,35; 21,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,35; 26,1</t>
+          <t>19,54; 25,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,85; 25,03</t>
+          <t>18,93; 25,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,91; 32,35</t>
+          <t>26,93; 32,2</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,82; 18,01</t>
+          <t>10,73; 18,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,23; 25,73</t>
+          <t>16,98; 25,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,82; 27,57</t>
+          <t>18,01; 27,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,27; 31,73</t>
+          <t>23,2; 30,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,95; 27,99</t>
+          <t>19,05; 27,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,96; 33,62</t>
+          <t>23,17; 33,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,92; 29,49</t>
+          <t>20,12; 29,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,61; 36,64</t>
+          <t>28,95; 36,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,84; 21,61</t>
+          <t>15,82; 21,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,49; 28,14</t>
+          <t>21,06; 27,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,09; 26,79</t>
+          <t>20,52; 26,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,04; 32,59</t>
+          <t>27,21; 32,57</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,03; 20,63</t>
+          <t>14,2; 20,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,76; 34,28</t>
+          <t>27,1; 34,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,02; 29,62</t>
+          <t>22,36; 29,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 34,73</t>
+          <t>8,18; 34,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,04; 34,74</t>
+          <t>20,94; 34,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,13; 43,51</t>
+          <t>31,95; 43,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,52; 46,74</t>
+          <t>31,74; 47,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,35; 58,9</t>
+          <t>46,18; 58,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,55; 22,31</t>
+          <t>16,82; 22,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,64; 36,24</t>
+          <t>29,37; 36,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,47; 32,4</t>
+          <t>25,35; 32,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,78; 39,75</t>
+          <t>13,05; 39,42</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,36; 24,19</t>
+          <t>19,51; 24,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,47; 31,9</t>
+          <t>26,18; 31,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,39; 27,42</t>
+          <t>22,42; 27,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,65; 38,28</t>
+          <t>31,64; 38,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,06; 29,28</t>
+          <t>22,81; 29,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,94; 37,12</t>
+          <t>29,69; 36,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,21; 30,57</t>
+          <t>24,36; 30,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,51; 74,57</t>
+          <t>37,33; 70,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,43; 25,24</t>
+          <t>21,41; 25,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,6; 32,97</t>
+          <t>28,59; 33,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,97; 27,88</t>
+          <t>23,93; 27,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,45; 58,35</t>
+          <t>35,65; 61,01</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,77; 21,87</t>
+          <t>13,91; 21,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,21; 29,83</t>
+          <t>22,47; 30,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,06; 29,13</t>
+          <t>22,2; 28,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,71; 37,63</t>
+          <t>28,67; 37,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,11; 32,76</t>
+          <t>24,95; 32,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,93; 50,55</t>
+          <t>43,35; 50,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,46; 44,89</t>
+          <t>37,84; 45,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,43; 49,58</t>
+          <t>32,56; 49,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,79; 27,48</t>
+          <t>21,75; 27,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35,36; 41,08</t>
+          <t>35,54; 41,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31,35; 36,62</t>
+          <t>31,47; 36,5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,63; 43,51</t>
+          <t>32,36; 43,33</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,46; 8,82</t>
+          <t>3,43; 8,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,08; 12,23</t>
+          <t>4,94; 12,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,34; 10,19</t>
+          <t>3,97; 10,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,87; 16,91</t>
+          <t>5,42; 16,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,71; 39,2</t>
+          <t>33,53; 38,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,39; 51,41</t>
+          <t>45,48; 51,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,9; 46,2</t>
+          <t>40,09; 46,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40,18; 46,83</t>
+          <t>40,26; 46,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28,2; 32,81</t>
+          <t>28,13; 32,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37,72; 43,13</t>
+          <t>37,77; 43,33</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32,6; 38,08</t>
+          <t>32,93; 38,33</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,07; 38,15</t>
+          <t>32,39; 38,81</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,2; 18,66</t>
+          <t>16,24; 18,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,64; 26,88</t>
+          <t>23,84; 26,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,59; 24,55</t>
+          <t>21,6; 24,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,14; 30,69</t>
+          <t>22,09; 30,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,25; 31,45</t>
+          <t>28,32; 31,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,11; 41,65</t>
+          <t>38,36; 41,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,03; 36,3</t>
+          <t>33,24; 36,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>39,23; 54,21</t>
+          <t>39,26; 53,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,79; 24,81</t>
+          <t>22,56; 24,7</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31,49; 33,9</t>
+          <t>31,62; 33,87</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,8; 30,13</t>
+          <t>27,87; 30,04</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32,12; 41,39</t>
+          <t>32,67; 42,43</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>63199; 96401</t>
+          <t>64594; 97754</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73970; 111423</t>
+          <t>74550; 112871</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76527; 113592</t>
+          <t>77313; 114515</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>122034; 162110</t>
+          <t>121639; 163134</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>56017; 83925</t>
+          <t>54253; 85608</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61885; 95693</t>
+          <t>61600; 95650</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61580; 93133</t>
+          <t>61664; 93075</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>124915; 157323</t>
+          <t>124548; 157462</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>125989; 171552</t>
+          <t>127602; 170517</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>145452; 196180</t>
+          <t>146848; 193388</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146273; 194277</t>
+          <t>146917; 195397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>256365; 308146</t>
+          <t>256539; 306718</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39714; 66094</t>
+          <t>39366; 67027</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72151; 107767</t>
+          <t>71110; 106007</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70987; 104003</t>
+          <t>67929; 101952</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>105239; 143495</t>
+          <t>104895; 139841</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>70461; 104091</t>
+          <t>70835; 103732</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77592; 113646</t>
+          <t>78309; 113982</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74159; 109779</t>
+          <t>74904; 108301</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>109462; 140183</t>
+          <t>110755; 141000</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>117037; 159661</t>
+          <t>116855; 159758</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>162622; 212976</t>
+          <t>159357; 209058</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>150574; 200760</t>
+          <t>153795; 200305</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>225709; 272053</t>
+          <t>227148; 271862</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>76095; 111896</t>
+          <t>77033; 111417</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>168420; 215749</t>
+          <t>170545; 218878</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>114928; 154568</t>
+          <t>116720; 155041</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50068; 232106</t>
+          <t>54696; 232750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>35297; 58292</t>
+          <t>35128; 58086</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80991; 113180</t>
+          <t>83115; 114046</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52363; 77643</t>
+          <t>52733; 78822</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>77371; 98305</t>
+          <t>77086; 97755</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>117499; 158441</t>
+          <t>119456; 162950</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>263677; 322341</t>
+          <t>261280; 320675</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>175221; 222941</t>
+          <t>174449; 225885</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>98391; 331964</t>
+          <t>108990; 329202</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>239745; 299572</t>
+          <t>241643; 301820</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>306781; 369726</t>
+          <t>303482; 368051</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>257354; 315215</t>
+          <t>257748; 316218</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>327500; 396113</t>
+          <t>327446; 394461</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>164713; 209142</t>
+          <t>162956; 210140</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>229508; 284589</t>
+          <t>227621; 282765</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>199981; 252463</t>
+          <t>201222; 254007</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>366877; 729400</t>
+          <t>365110; 693345</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>418494; 492779</t>
+          <t>417959; 491417</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>550721; 634977</t>
+          <t>550572; 637495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>473436; 550712</t>
+          <t>472704; 551341</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>713541; 1174603</t>
+          <t>717632; 1228102</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>48276; 76669</t>
+          <t>48777; 76099</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>113415; 152299</t>
+          <t>114716; 153916</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136943; 180811</t>
+          <t>137785; 179465</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136378; 178737</t>
+          <t>136196; 179294</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>142799; 186298</t>
+          <t>141897; 187055</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>326893; 384955</t>
+          <t>330090; 385372</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>276583; 331380</t>
+          <t>279317; 332671</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>264407; 417114</t>
+          <t>273947; 419806</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>200326; 252665</t>
+          <t>199991; 254203</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>449819; 522622</t>
+          <t>452171; 523690</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>426008; 497697</t>
+          <t>427630; 495954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>429518; 572822</t>
+          <t>425966; 570399</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10320; 26314</t>
+          <t>10215; 26010</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13548; 32641</t>
+          <t>13179; 32761</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12460; 29247</t>
+          <t>11396; 28956</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11706; 40667</t>
+          <t>13033; 40039</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>421013; 489548</t>
+          <t>418682; 486354</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>503510; 570276</t>
+          <t>504572; 569457</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>431748; 499907</t>
+          <t>433774; 503281</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>305946; 356517</t>
+          <t>306542; 357213</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>436256; 507520</t>
+          <t>435135; 509440</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>519054; 593548</t>
+          <t>519858; 596259</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>446299; 521418</t>
+          <t>450936; 524790</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>321342; 382234</t>
+          <t>324488; 388852</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>529650; 610366</t>
+          <t>531241; 616328</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>809013; 919920</t>
+          <t>815915; 922354</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>730826; 831196</t>
+          <t>731167; 828832</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>713594; 1036034</t>
+          <t>745908; 1030521</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>954313; 1062304</t>
+          <t>956852; 1060443</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1352936; 1478671</t>
+          <t>1361852; 1481394</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1166568; 1282080</t>
+          <t>1173916; 1289227</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1403568; 1939646</t>
+          <t>1404528; 1918810</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1515455; 1649740</t>
+          <t>1499621; 1641852</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2195565; 2363707</t>
+          <t>2204525; 2361372</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1923225; 2084150</t>
+          <t>1927768; 2078101</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2233513; 2878464</t>
+          <t>2271523; 2950347</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_n_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R2-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,63; 20,63</t>
+          <t>13,49; 20,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,05; 25,82</t>
+          <t>17,3; 25,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,02; 26,69</t>
+          <t>17,93; 26,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,08; 32,29</t>
+          <t>24,01; 31,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,69; 27,91</t>
+          <t>18,57; 27,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,59; 30,42</t>
+          <t>20,04; 30,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,77; 26,82</t>
+          <t>17,59; 26,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,83; 35,19</t>
+          <t>27,63; 34,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,35; 21,85</t>
+          <t>16,39; 22,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,54; 25,73</t>
+          <t>19,55; 25,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,93; 25,18</t>
+          <t>19,24; 25,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,93; 32,2</t>
+          <t>26,91; 32,29</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,73; 18,27</t>
+          <t>10,29; 18,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,98; 25,31</t>
+          <t>16,99; 25,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,01; 27,03</t>
+          <t>18,36; 27,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,2; 30,92</t>
+          <t>23,21; 31,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,05; 27,9</t>
+          <t>19,11; 27,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,17; 33,72</t>
+          <t>23,54; 33,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,12; 29,09</t>
+          <t>19,98; 29,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,95; 36,85</t>
+          <t>28,65; 36,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,82; 21,62</t>
+          <t>15,79; 21,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,06; 27,62</t>
+          <t>21,06; 27,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,52; 26,73</t>
+          <t>20,33; 26,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,21; 32,57</t>
+          <t>26,96; 32,29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,2; 20,54</t>
+          <t>14,42; 20,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,1; 34,77</t>
+          <t>27,23; 34,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,36; 29,71</t>
+          <t>22,16; 29,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,18; 34,83</t>
+          <t>28,38; 36,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,94; 34,62</t>
+          <t>20,72; 34,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,95; 43,84</t>
+          <t>31,65; 44,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,74; 47,45</t>
+          <t>31,13; 47,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,18; 58,57</t>
+          <t>45,4; 57,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,82; 22,95</t>
+          <t>16,8; 22,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,37; 36,05</t>
+          <t>29,56; 35,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,35; 32,83</t>
+          <t>25,57; 32,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,05; 39,42</t>
+          <t>34,03; 41,21</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>36,11%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,51; 24,37</t>
+          <t>19,47; 24,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,18; 31,76</t>
+          <t>26,04; 31,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,42; 27,51</t>
+          <t>22,37; 27,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,64; 38,12</t>
+          <t>31,46; 37,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,81; 29,42</t>
+          <t>23,16; 29,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,69; 36,88</t>
+          <t>30,13; 37,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,36; 30,76</t>
+          <t>24,15; 30,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,33; 70,89</t>
+          <t>35,61; 41,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,41; 25,17</t>
+          <t>21,46; 25,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,59; 33,11</t>
+          <t>28,54; 32,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,93; 27,91</t>
+          <t>23,82; 27,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,65; 61,01</t>
+          <t>34,07; 38,11</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>41,16%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,91; 21,71</t>
+          <t>13,86; 22,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,47; 30,14</t>
+          <t>22,01; 30,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,2; 28,91</t>
+          <t>22,42; 29,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,67; 37,74</t>
+          <t>27,25; 35,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,95; 32,89</t>
+          <t>25,48; 33,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,35; 50,61</t>
+          <t>42,93; 50,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,84; 45,06</t>
+          <t>37,48; 45,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,56; 49,9</t>
+          <t>45,22; 51,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,75; 27,65</t>
+          <t>21,82; 27,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35,54; 41,17</t>
+          <t>35,7; 40,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31,47; 36,5</t>
+          <t>31,48; 36,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,36; 43,33</t>
+          <t>38,97; 43,64</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,43; 8,72</t>
+          <t>3,22; 8,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,94; 12,28</t>
+          <t>4,95; 12,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,97; 10,08</t>
+          <t>4,11; 10,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,42; 16,65</t>
+          <t>5,69; 17,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,53; 38,95</t>
+          <t>33,82; 39,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,48; 51,33</t>
+          <t>45,13; 51,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,09; 46,51</t>
+          <t>40,1; 46,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40,26; 46,92</t>
+          <t>39,49; 45,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28,13; 32,93</t>
+          <t>27,91; 32,74</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37,77; 43,33</t>
+          <t>37,57; 42,96</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32,93; 38,33</t>
+          <t>33,1; 38,61</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,39; 38,81</t>
+          <t>32,4; 38,08</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,24; 18,85</t>
+          <t>16,19; 18,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,84; 26,95</t>
+          <t>23,76; 26,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,6; 24,48</t>
+          <t>21,4; 24,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,09; 30,52</t>
+          <t>28,09; 31,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,32; 31,39</t>
+          <t>28,22; 31,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,36; 41,73</t>
+          <t>38,2; 41,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,24; 36,51</t>
+          <t>33,07; 36,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>39,26; 53,63</t>
+          <t>39,14; 41,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,56; 24,7</t>
+          <t>22,65; 24,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31,62; 33,87</t>
+          <t>31,71; 33,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,87; 30,04</t>
+          <t>27,85; 30,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32,67; 42,43</t>
+          <t>34,2; 36,35</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>140993</t>
+          <t>153134</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>140519</t>
+          <t>151492</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>281512</t>
+          <t>304626</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>64594; 97754</t>
+          <t>63932; 98159</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>74550; 112871</t>
+          <t>75642; 111111</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77313; 114515</t>
+          <t>76928; 112912</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>121639; 163134</t>
+          <t>132188; 173082</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>54253; 85608</t>
+          <t>56951; 85004</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61600; 95650</t>
+          <t>63012; 94331</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61664; 93075</t>
+          <t>61053; 92513</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>124548; 157462</t>
+          <t>134968; 169593</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>127602; 170517</t>
+          <t>127944; 172130</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>146848; 193388</t>
+          <t>146958; 194684</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146917; 195397</t>
+          <t>149348; 195788</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>256539; 306718</t>
+          <t>279624; 335498</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>122317</t>
+          <t>130760</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>125734</t>
+          <t>136776</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>248051</t>
+          <t>267536</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39366; 67027</t>
+          <t>37743; 66058</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71110; 106007</t>
+          <t>71143; 108150</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67929; 101952</t>
+          <t>69244; 102821</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>104895; 139841</t>
+          <t>112162; 149958</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>70835; 103732</t>
+          <t>71070; 102659</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78309; 113982</t>
+          <t>79558; 113873</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74904; 108301</t>
+          <t>74362; 109532</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>110755; 141000</t>
+          <t>121217; 153835</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>116855; 159758</t>
+          <t>116624; 158839</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>159357; 209058</t>
+          <t>159379; 211102</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>153795; 200305</t>
+          <t>152381; 199583</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>227148; 271862</t>
+          <t>244365; 292695</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141667</t>
+          <t>151486</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>87089</t>
+          <t>96274</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>228756</t>
+          <t>247760</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>77033; 111417</t>
+          <t>78225; 111916</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>170545; 218878</t>
+          <t>171418; 218778</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>116720; 155041</t>
+          <t>115634; 154343</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54696; 232750</t>
+          <t>133834; 173043</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>35128; 58086</t>
+          <t>34759; 57540</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83115; 114046</t>
+          <t>82325; 114516</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52733; 78822</t>
+          <t>51714; 79037</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>77086; 97755</t>
+          <t>85131; 108348</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>119456; 162950</t>
+          <t>119303; 159897</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>261280; 320675</t>
+          <t>262970; 319357</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>174449; 225885</t>
+          <t>175906; 223561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>108990; 329202</t>
+          <t>224279; 271600</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358351</t>
+          <t>390771</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>502045</t>
+          <t>328892</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>860395</t>
+          <t>719663</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>241643; 301820</t>
+          <t>241057; 298010</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>303482; 368051</t>
+          <t>301773; 367456</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>257748; 316218</t>
+          <t>257148; 315306</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>327446; 394461</t>
+          <t>356047; 423927</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>162956; 210140</t>
+          <t>165461; 210385</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>227621; 282765</t>
+          <t>231025; 287857</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>201222; 254007</t>
+          <t>199462; 250385</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>365110; 693345</t>
+          <t>306677; 355343</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>417959; 491417</t>
+          <t>418965; 489661</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>550572; 637495</t>
+          <t>549601; 635320</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>472704; 551341</t>
+          <t>470540; 549583</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>717632; 1228102</t>
+          <t>679059; 759505</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156828</t>
+          <t>176260</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>366475</t>
+          <t>399519</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>523303</t>
+          <t>575780</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>48777; 76099</t>
+          <t>48581; 77182</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>114716; 153916</t>
+          <t>112388; 153537</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>137785; 179465</t>
+          <t>139173; 182068</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136196; 179294</t>
+          <t>154750; 199410</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>141897; 187055</t>
+          <t>144915; 188470</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>330090; 385372</t>
+          <t>326919; 384859</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>279317; 332671</t>
+          <t>276662; 333178</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>273947; 419806</t>
+          <t>375739; 424430</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>199991; 254203</t>
+          <t>200611; 253651</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>452171; 523690</t>
+          <t>454088; 521364</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>427630; 495954</t>
+          <t>427779; 495108</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>425966; 570399</t>
+          <t>545118; 610423</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23099</t>
+          <t>24472</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>331619</t>
+          <t>358347</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>354718</t>
+          <t>382820</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10215; 26010</t>
+          <t>9603; 25695</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13179; 32761</t>
+          <t>13207; 32323</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11396; 28956</t>
+          <t>11809; 29826</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13033; 40039</t>
+          <t>13489; 42098</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>418682; 486354</t>
+          <t>422347; 487802</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>504572; 569457</t>
+          <t>500598; 570907</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>433774; 503281</t>
+          <t>433941; 501184</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>306542; 357213</t>
+          <t>333404; 385824</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>435135; 509440</t>
+          <t>431807; 506492</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>519858; 596259</t>
+          <t>517043; 591270</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>450936; 524790</t>
+          <t>453259; 528610</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>324488; 388852</t>
+          <t>350381; 411882</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>943254</t>
+          <t>1026884</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1553481</t>
+          <t>1471300</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2496735</t>
+          <t>2498184</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>531241; 616328</t>
+          <t>529316; 611582</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>815915; 922354</t>
+          <t>812973; 919965</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>731167; 828832</t>
+          <t>724506; 829541</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>745908; 1030521</t>
+          <t>966937; 1086289</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>956852; 1060443</t>
+          <t>953366; 1060286</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1361852; 1481394</t>
+          <t>1356258; 1479517</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1173916; 1289227</t>
+          <t>1167923; 1285810</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1404528; 1918810</t>
+          <t>1423024; 1523111</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1499621; 1641852</t>
+          <t>1505573; 1649696</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2204525; 2361372</t>
+          <t>2210707; 2366671</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1927768; 2078101</t>
+          <t>1926296; 2079915</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2271523; 2950347</t>
+          <t>2420718; 2572646</t>
         </is>
       </c>
     </row>
